--- a/www/download/IND.surplus_value.empe.r.pc.rpA2.xlsx
+++ b/www/download/IND.surplus_value.empe.r.pc.rpA2.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Alternative 2</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,84 +688,84 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>105.32</t>
+          <t>1.0532128229841</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>97.87</t>
+          <t>0.978676857313621</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>107.46</t>
+          <t>1.07461011886338</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>108.57</t>
+          <t>1.08573663828902</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>96.61</t>
+          <t>0.966134701460474</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>104.96</t>
+          <t>1.04956792209913</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>109.44</t>
+          <t>1.09442495039842</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>101.76</t>
+          <t>1.01755181253153</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>91.55</t>
+          <t>0.915465996064372</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>67.29</t>
+          <t>0.672894117008444</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>59.82</t>
+          <t>0.598159025261831</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>62.62</t>
+          <t>0.626228335898959</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>58.77</t>
+          <t>0.58770115722692</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>0.711044868738588</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>76.65</t>
+          <t>0.766538848797931</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,84 +775,84 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>35.73</t>
+          <t>0.357257633370238</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>39.44</t>
+          <t>0.394355382823285</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>62.28</t>
+          <t>0.622770351210551</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>60.22</t>
+          <t>0.602193106039567</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>61.3</t>
+          <t>0.612975036260835</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>68.58</t>
+          <t>0.685756166139305</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>66.66</t>
+          <t>0.666574984869162</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>63.57</t>
+          <t>0.635728268291599</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>51.05</t>
+          <t>0.510537745537083</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>49.03</t>
+          <t>0.490304504012592</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>47.29</t>
+          <t>0.47291795657629</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>44.87</t>
+          <t>0.448749234480762</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>45.08</t>
+          <t>0.450789910778949</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>50.49</t>
+          <t>0.504891739376469</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>60.34</t>
+          <t>0.603428007086523</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -857,84 +862,84 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>0.0259306144199154</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.00923075493601355</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>7.71</t>
+          <t>0.0771083669061059</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>8.26</t>
+          <t>0.0825749535680445</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.00375374774583304</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-2.48</t>
+          <t>-0.0247868685475643</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-7.85</t>
+          <t>-0.0784778064164131</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-15.3</t>
+          <t>-0.152980933788753</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>-30.36</t>
+          <t>-0.303556272991232</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-32.59</t>
+          <t>-0.325876403364135</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>-30.94</t>
+          <t>-0.309437778890024</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>-29.36</t>
+          <t>-0.293606453520773</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>-25.97</t>
+          <t>-0.259741948721863</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>-16.06</t>
+          <t>-0.160621822740825</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>-20.5</t>
+          <t>-0.205010426901766</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -944,84 +949,84 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>365.89</t>
+          <t>3.65894030523879</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>412.02</t>
+          <t>4.12023234717778</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>483.78</t>
+          <t>4.83775382042288</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>343.82</t>
+          <t>3.43819167811752</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>376.04</t>
+          <t>3.76035657023825</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>417.28</t>
+          <t>4.17276235962103</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>408.89</t>
+          <t>4.088871169689</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>412.22</t>
+          <t>4.12222044185029</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>420.7</t>
+          <t>4.20696441397113</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>438.53</t>
+          <t>4.38530550046149</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>462.65</t>
+          <t>4.62650684184424</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>465.98</t>
+          <t>4.6597510399776</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>423.5</t>
+          <t>4.23497319836877</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>375.46</t>
+          <t>3.75461432716296</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>326.87</t>
+          <t>3.26869684835973</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1031,84 +1036,84 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>253.67</t>
+          <t>2.53668910932279</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>252.94</t>
+          <t>2.52936760201301</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>273.76</t>
+          <t>2.73757115953293</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>270.77</t>
+          <t>2.7076710724593</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>306.27</t>
+          <t>3.06273571738657</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>314.97</t>
+          <t>3.14966378109465</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>328.44</t>
+          <t>3.28443379682983</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>346.58</t>
+          <t>3.4657554688907</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>355.12</t>
+          <t>3.55119300854594</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>347.72</t>
+          <t>3.47720583481405</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>334.11</t>
+          <t>3.34113109398516</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>329.37</t>
+          <t>3.29370950727922</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>326.55</t>
+          <t>3.26551998283224</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>311.34</t>
+          <t>3.11336010639105</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>320.18</t>
+          <t>3.20175199506288</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1118,84 +1123,84 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>176.94</t>
+          <t>1.76940602500324</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>183.83</t>
+          <t>1.8382698901191</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>199.62</t>
+          <t>1.99616963676183</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>185.08</t>
+          <t>1.85078422785115</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>173.61</t>
+          <t>1.73610313054803</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>153.31</t>
+          <t>1.53307754112019</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>139.87</t>
+          <t>1.3986750616682</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>139.96</t>
+          <t>1.39960022645412</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>127.29</t>
+          <t>1.27288790472861</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>119.05</t>
+          <t>1.19049819518018</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>107.14</t>
+          <t>1.07144658914383</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>101.65</t>
+          <t>1.01652748443302</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>109.47</t>
+          <t>1.09474858033803</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>109.81</t>
+          <t>1.09810397592225</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>126.03</t>
+          <t>1.26034328500752</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,84 +1210,84 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-9.61</t>
+          <t>-0.0961445644302295</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>-4.47</t>
+          <t>-0.0447171666969939</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-0.0153931121465996</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>0.024457501479018</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>0.0749735572848782</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>16.05</t>
+          <t>0.160503307477327</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>28.61</t>
+          <t>0.286065087053998</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>38.45</t>
+          <t>0.384489171843214</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>48.13</t>
+          <t>0.481337176829741</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>55.63</t>
+          <t>0.556265355307095</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>63.83</t>
+          <t>0.638286274074408</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>66.95</t>
+          <t>0.669505405117084</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>83.92</t>
+          <t>0.839222028399555</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>0.845023733680335</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>89.56</t>
+          <t>0.895569023385382</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1292,84 +1297,84 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>180.74</t>
+          <t>1.80740953711676</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>181.87</t>
+          <t>1.81873380163862</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>215.65</t>
+          <t>2.15652249932171</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>194.29</t>
+          <t>1.94292155534419</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>175.97</t>
+          <t>1.75969462271262</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>181.24</t>
+          <t>1.81239393672407</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>164.95</t>
+          <t>1.64946186551978</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>156.9</t>
+          <t>1.56899989833196</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>129.01</t>
+          <t>1.2900845427379</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>134.56</t>
+          <t>1.3455928874396</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>139.01</t>
+          <t>1.3900735038774</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>149.65</t>
+          <t>1.4964835979432</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>176.56</t>
+          <t>1.7655781062828</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>146.8</t>
+          <t>1.46796960452735</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>190.96</t>
+          <t>1.90963057469608</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,84 +1384,84 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>466.61</t>
+          <t>4.666139976184</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>299.52</t>
+          <t>2.99521991602889</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>327.61</t>
+          <t>3.27605811337549</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>320.29</t>
+          <t>3.20288341445275</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>325.29</t>
+          <t>3.25293597753306</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>339.62</t>
+          <t>3.39619752490449</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>307.64</t>
+          <t>3.07641043845268</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>291.34</t>
+          <t>2.91340353190965</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>261.39</t>
+          <t>2.61393965164959</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>243.53</t>
+          <t>2.43533638764963</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>233.18</t>
+          <t>2.33184421472736</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>244.17</t>
+          <t>2.44171941673897</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>239.66</t>
+          <t>2.39655186137134</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>248.01</t>
+          <t>2.48012329884068</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>294.82</t>
+          <t>2.94818361720181</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1466,84 +1471,84 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>37.81</t>
+          <t>0.378132642556137</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>0.48801794126004</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>67.29</t>
+          <t>0.672867062316342</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>64.04</t>
+          <t>0.640386219629592</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>58.41</t>
+          <t>0.584072307198068</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>51.46</t>
+          <t>0.514632369052465</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>54.11</t>
+          <t>0.541105509924911</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>52.17</t>
+          <t>0.521749964484292</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>35.87</t>
+          <t>0.358662387258665</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>35.51</t>
+          <t>0.355117928126402</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>39.61</t>
+          <t>0.396090541227027</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>38.24</t>
+          <t>0.382394339124414</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>36.37</t>
+          <t>0.363679349453728</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>43.78</t>
+          <t>0.437829694917139</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>48.85</t>
+          <t>0.48853232479938</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1553,84 +1558,84 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>35.03</t>
+          <t>0.350311772755886</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>37.57</t>
+          <t>0.375662274440565</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>71.96</t>
+          <t>0.719623073784208</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>62.32</t>
+          <t>0.623247812150844</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>62.31</t>
+          <t>0.623098865025758</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>69.55</t>
+          <t>0.69553925406173</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>62.93</t>
+          <t>0.629278357328959</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>56.53</t>
+          <t>0.56529310554358</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>0.39103372734961</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>38.17</t>
+          <t>0.381744117412144</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>39.88</t>
+          <t>0.398842128100096</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>40.53</t>
+          <t>0.405254806478792</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>33.45</t>
+          <t>0.33451766091841</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>43.44</t>
+          <t>0.434384869546108</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>54.85</t>
+          <t>0.548499270146898</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1640,84 +1645,84 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>94.9</t>
+          <t>0.948996846436659</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>106.73</t>
+          <t>1.06732164536696</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>144.57</t>
+          <t>1.44573470852071</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>127.92</t>
+          <t>1.27917305121842</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>118.54</t>
+          <t>1.18537387731512</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>128.08</t>
+          <t>1.28081106090263</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>119.6</t>
+          <t>1.1959808164592</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>109.52</t>
+          <t>1.09523789065721</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>91.43</t>
+          <t>0.914337114940346</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>86.52</t>
+          <t>0.865199645939472</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>88.39</t>
+          <t>0.88392062713498</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>85.39</t>
+          <t>0.853850691659189</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>87.12</t>
+          <t>0.871218606311629</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>90.44</t>
+          <t>0.904424281448636</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>112.86</t>
+          <t>1.12856799574791</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1727,84 +1732,84 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>433.85</t>
+          <t>4.33850727271121</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>413.72</t>
+          <t>4.13716833539566</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>404.89</t>
+          <t>4.04888376736428</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>377.62</t>
+          <t>3.77617621510672</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>376.84</t>
+          <t>3.76835511793134</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>322.48</t>
+          <t>3.22477909583087</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>333.2</t>
+          <t>3.33200651464128</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>253.88</t>
+          <t>2.53883027778843</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>203.63</t>
+          <t>2.0362576960364</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>195.17</t>
+          <t>1.95169806567925</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>226.49</t>
+          <t>2.26494528601573</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>232.6</t>
+          <t>2.32596437727155</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>220.48</t>
+          <t>2.20478338710204</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>191.23</t>
+          <t>1.91225519166841</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>202.6</t>
+          <t>2.0260383746118</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1814,84 +1819,84 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>101.77</t>
+          <t>1.01765632870154</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>100.24</t>
+          <t>1.00238442524852</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>136.88</t>
+          <t>1.36882227404002</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>121.88</t>
+          <t>1.21881311492904</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>118.5</t>
+          <t>1.18504574738128</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>137.37</t>
+          <t>1.37370323526383</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>131.71</t>
+          <t>1.31705076251179</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>130.38</t>
+          <t>1.30383550197755</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>110.57</t>
+          <t>1.10573140336455</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>102.65</t>
+          <t>1.02646595837558</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>99.33</t>
+          <t>0.993295107541721</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>96.18</t>
+          <t>0.961782916825531</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>98.55</t>
+          <t>0.985543707785101</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>101.29</t>
+          <t>1.01286998339127</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>112.07</t>
+          <t>1.12073594129139</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1901,84 +1906,84 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>77.22</t>
+          <t>0.772242707197384</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>73.35</t>
+          <t>0.733519147370481</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>101.63</t>
+          <t>1.01634464540444</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>85.19</t>
+          <t>0.851939328857213</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>75.09</t>
+          <t>0.750862541844112</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>75.41</t>
+          <t>0.75411852878486</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>67.15</t>
+          <t>0.671513390972636</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>58.26</t>
+          <t>0.582581200935456</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>44.7</t>
+          <t>0.446978197014652</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>42.12</t>
+          <t>0.421204333730701</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>43.51</t>
+          <t>0.435130251717724</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>47.46</t>
+          <t>0.474625890245324</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>0.509959246909197</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>0.560025457147041</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>68.54</t>
+          <t>0.68539028870186</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1988,84 +1993,84 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>125.52</t>
+          <t>1.25519480244501</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>123.13</t>
+          <t>1.23132405757834</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>143.44</t>
+          <t>1.4344117129802</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>127.63</t>
+          <t>1.27629877757849</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>118.22</t>
+          <t>1.18222819609277</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>111.65</t>
+          <t>1.11650695920428</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>102.89</t>
+          <t>1.02888859906627</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>96.84</t>
+          <t>0.968418616858238</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>84.32</t>
+          <t>0.843154497449138</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>75.18</t>
+          <t>0.751834283533135</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>77.26</t>
+          <t>0.772641012898869</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>77.47</t>
+          <t>0.774731922957285</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>0.825982194522748</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>103.68</t>
+          <t>1.03677209029592</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>121.26</t>
+          <t>1.21255854575187</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2075,84 +2080,84 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>237.88</t>
+          <t>2.37880068149996</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>224.84</t>
+          <t>2.24844378413753</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>235.45</t>
+          <t>2.35452250954127</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>240.88</t>
+          <t>2.40877028367542</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>225.87</t>
+          <t>2.25872141207475</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>211.05</t>
+          <t>2.11049698318507</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>223.41</t>
+          <t>2.23406150573122</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>187.09</t>
+          <t>1.87090557077448</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>179.59</t>
+          <t>1.7959198345048</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>180.21</t>
+          <t>1.80205324579841</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>187.1</t>
+          <t>1.8709731224922</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>185.33</t>
+          <t>1.85334431620349</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>171.35</t>
+          <t>1.71349972788208</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>167.26</t>
+          <t>1.67257236559777</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>162.4</t>
+          <t>1.62403957964167</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2162,84 +2167,84 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>215.54</t>
+          <t>2.15536383353231</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>230.57</t>
+          <t>2.30571252755721</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>252.81</t>
+          <t>2.52811629709757</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>263.35</t>
+          <t>2.63349678534225</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>261.83</t>
+          <t>2.61829859289064</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>260.45</t>
+          <t>2.60448250688261</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>275.08</t>
+          <t>2.75081088791863</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>249.48</t>
+          <t>2.49480188405092</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>228.92</t>
+          <t>2.28921675630798</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>274.26</t>
+          <t>2.74256558762617</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>279.33</t>
+          <t>2.79327306532723</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>300.41</t>
+          <t>3.00407229789527</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>287.81</t>
+          <t>2.8780864806403</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>322.36</t>
+          <t>3.22362949642588</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>347.14</t>
+          <t>3.47137139544891</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2249,84 +2254,84 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>157.17</t>
+          <t>1.57174149024764</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>171.31</t>
+          <t>1.71305400866255</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>206.2</t>
+          <t>2.06202798627357</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>246.95</t>
+          <t>2.46947865793587</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>268.48</t>
+          <t>2.6848220484862</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>232.62</t>
+          <t>2.32624154987493</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>219.71</t>
+          <t>2.19706769541516</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>215.68</t>
+          <t>2.15679197401425</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>191.72</t>
+          <t>1.91719516179833</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>195.21</t>
+          <t>1.95210387516067</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>172.67</t>
+          <t>1.72667517968717</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>167.07</t>
+          <t>1.67071499722966</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>143.91</t>
+          <t>1.43907239443529</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>150.23</t>
+          <t>1.50229549998294</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>147.12</t>
+          <t>1.47121155843777</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2336,84 +2341,84 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>72.31</t>
+          <t>0.72311905419033</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>88.7</t>
+          <t>0.887002166751777</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>79.52</t>
+          <t>0.795201345674204</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>82.24</t>
+          <t>0.822407308988612</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>85.96</t>
+          <t>0.859629105843602</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>89.94</t>
+          <t>0.899443948231848</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>0.884993857221793</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>93.51</t>
+          <t>0.935131541006065</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>85.88</t>
+          <t>0.858825549207736</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>79.58</t>
+          <t>0.795789007562876</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>74.6</t>
+          <t>0.74596776455455</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>71.49</t>
+          <t>0.714928348863544</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>0.762970913758579</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>82.1</t>
+          <t>0.82099046095278</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>75.08</t>
+          <t>0.750835637882481</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2423,84 +2428,84 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>115.99</t>
+          <t>1.15986209597812</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>117.45</t>
+          <t>1.17445736718002</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>146.03</t>
+          <t>1.4602573424597</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>160.25</t>
+          <t>1.60245213791576</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>163.31</t>
+          <t>1.63306797661556</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>161.57</t>
+          <t>1.61572057347105</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>138.84</t>
+          <t>1.38838036526565</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>131.45</t>
+          <t>1.31449908900932</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>153.83</t>
+          <t>1.53834895501998</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>168.94</t>
+          <t>1.68942180703257</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>151.67</t>
+          <t>1.51666282874503</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>156.74</t>
+          <t>1.56737025474678</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>133.53</t>
+          <t>1.33533022909171</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>126.63</t>
+          <t>1.26630331054188</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>110.15</t>
+          <t>1.10146970343049</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2510,84 +2515,84 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>69.12</t>
+          <t>0.691219282159373</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>72.61</t>
+          <t>0.726082414457233</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>91.27</t>
+          <t>0.912686357530926</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>93.28</t>
+          <t>0.932818835288297</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>92.14</t>
+          <t>0.921378372879522</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>93.37</t>
+          <t>0.933743778831401</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>83.55</t>
+          <t>0.835458282262771</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>77.01</t>
+          <t>0.770114109640439</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>61.55</t>
+          <t>0.615481999462696</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>52.06</t>
+          <t>0.520576787664462</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>54.29</t>
+          <t>0.54290680290115</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>52.99</t>
+          <t>0.529935262807366</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>61.42</t>
+          <t>0.614231951002822</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>73.42</t>
+          <t>0.734151424680189</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>87.27</t>
+          <t>0.872677433279726</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2597,84 +2602,84 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>98.48</t>
+          <t>0.984823255892516</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>121.64</t>
+          <t>1.21637486524701</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>144.67</t>
+          <t>1.4467433604077</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>150.4</t>
+          <t>1.50396060207041</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>134.1</t>
+          <t>1.34103003578273</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>125.34</t>
+          <t>1.25336717884525</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>128.54</t>
+          <t>1.28536183629686</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>136.73</t>
+          <t>1.3673023298218</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>134.64</t>
+          <t>1.34637813478269</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>124.07</t>
+          <t>1.24067039969177</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>123.6</t>
+          <t>1.23602588757475</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>133.08</t>
+          <t>1.33078426118789</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>151.56</t>
+          <t>1.5156254835241</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>149.96</t>
+          <t>1.49961980160608</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>136.09</t>
+          <t>1.36085403244736</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,84 +2689,84 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>117.44</t>
+          <t>1.17437561111754</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>127.37</t>
+          <t>1.27367316791224</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>149.34</t>
+          <t>1.49338938739643</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>159.53</t>
+          <t>1.59529994333408</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>178.53</t>
+          <t>1.78530018837607</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>166.87</t>
+          <t>1.66867131822774</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>172.03</t>
+          <t>1.72031779272466</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>182.43</t>
+          <t>1.82431743641831</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>169.03</t>
+          <t>1.69028136388492</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>170.32</t>
+          <t>1.7031550108083</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>172.21</t>
+          <t>1.72209245205036</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>165.41</t>
+          <t>1.6541291328505</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>171.81</t>
+          <t>1.7181173404617</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>187.24</t>
+          <t>1.87244743555695</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>188.94</t>
+          <t>1.88940586628861</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2771,84 +2776,84 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>369.74</t>
+          <t>3.69736620911936</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>348.81</t>
+          <t>3.48808883227878</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>343.08</t>
+          <t>3.43083816326461</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>275.26</t>
+          <t>2.75256343917978</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>256.13</t>
+          <t>2.56126584726751</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>270.65</t>
+          <t>2.70650083950323</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>279.23</t>
+          <t>2.79229419644174</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>262.89</t>
+          <t>2.62889311821161</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>236.06</t>
+          <t>2.36056275170388</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>284.85</t>
+          <t>2.8485111680157</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>280.25</t>
+          <t>2.80247155474506</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>269.71</t>
+          <t>2.69706412096064</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>283.35</t>
+          <t>2.83345542270438</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>266.84</t>
+          <t>2.66840268048593</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>276.48</t>
+          <t>2.76483594673552</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2858,84 +2863,84 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>0.406047974737331</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>58.64</t>
+          <t>0.586431041482539</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>90.67</t>
+          <t>0.906654742879437</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>95.39</t>
+          <t>0.953908927935007</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>91.48</t>
+          <t>0.914773063459074</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>87.91</t>
+          <t>0.879141584722622</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>100.82</t>
+          <t>1.00822711126514</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>86.32</t>
+          <t>0.863221376354964</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>60.91</t>
+          <t>0.609067367452899</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>0.813028320574295</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>77.97</t>
+          <t>0.779705271311993</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>0.766969469908587</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>102.45</t>
+          <t>1.02454001632638</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>82.57</t>
+          <t>0.825686305986852</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>126.06</t>
+          <t>1.2606468661908</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,84 +2950,84 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>374.6</t>
+          <t>3.74602860731114</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>357.14</t>
+          <t>3.57137216684786</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>353.81</t>
+          <t>3.53810668156894</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>352.37</t>
+          <t>3.52372324552785</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>346.1</t>
+          <t>3.46096227065715</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>409.44</t>
+          <t>4.09440867965834</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>424.72</t>
+          <t>4.24717362060655</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>445.28</t>
+          <t>4.45283395555601</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>407.63</t>
+          <t>4.07633571133498</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>413.47</t>
+          <t>4.13470226161728</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>384.29</t>
+          <t>3.84293725562199</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>345.16</t>
+          <t>3.45157756669306</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>303.22</t>
+          <t>3.03217086054479</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>264.12</t>
+          <t>2.64115203625528</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>304.84</t>
+          <t>3.04844741415563</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3032,84 +3037,84 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>394.66</t>
+          <t>3.94660515907954</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>420.81</t>
+          <t>4.20813902887508</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>439.9</t>
+          <t>4.39895434200082</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>405.58</t>
+          <t>4.05576652027345</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>384.39</t>
+          <t>3.84393745401302</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>371.84</t>
+          <t>3.71837242660241</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>327.77</t>
+          <t>3.27768624576948</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>330.54</t>
+          <t>3.30536135820461</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>338.15</t>
+          <t>3.38150449833357</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>352.31</t>
+          <t>3.52314959161206</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>358.13</t>
+          <t>3.5812670983585</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>375.29</t>
+          <t>3.75287972011037</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>3.90002685844947</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>404.91</t>
+          <t>4.04913386802377</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>408.67</t>
+          <t>4.0866807259061</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3119,84 +3124,84 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>144.75</t>
+          <t>1.4475150159286</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>127.15</t>
+          <t>1.27148460522877</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>173.03</t>
+          <t>1.73028390593478</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>145.1</t>
+          <t>1.45103926657973</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>116.34</t>
+          <t>1.16343766155602</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>103.65</t>
+          <t>1.03653091717413</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>53.62</t>
+          <t>0.536247890203575</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>68.94</t>
+          <t>0.689374537161907</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>51.56</t>
+          <t>0.515599788972781</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>103.34</t>
+          <t>1.03344511803101</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>100.06</t>
+          <t>1.00057622623835</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>108.61</t>
+          <t>1.08611372206193</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>96.78</t>
+          <t>0.967758665477225</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>80.12</t>
+          <t>0.801206708620414</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>107.43</t>
+          <t>1.07426239407753</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3206,84 +3211,84 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>7.71</t>
+          <t>0.0771068627696603</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>13.57</t>
+          <t>0.135727279934285</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>65.38</t>
+          <t>0.653832253597852</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>37.62</t>
+          <t>0.376193351316239</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>36.66</t>
+          <t>0.36663079036316</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>33.64</t>
+          <t>0.336433537241412</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>19.97</t>
+          <t>0.199715140724557</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>9.59</t>
+          <t>0.0958631727564834</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>13.05</t>
+          <t>0.130471762059363</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>15.83</t>
+          <t>0.158277217146407</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>0.203521927925106</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>21.34</t>
+          <t>0.213354842288687</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>21.67</t>
+          <t>0.216726654981916</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>15.84</t>
+          <t>0.15835210214361</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>18.47</t>
+          <t>0.184743099008181</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3293,84 +3298,84 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>146.28</t>
+          <t>1.46282514272786</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>134.77</t>
+          <t>1.3476835532343</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>130.41</t>
+          <t>1.30408588839403</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>126.6</t>
+          <t>1.26600748654529</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>147.93</t>
+          <t>1.4792574453321</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>162.24</t>
+          <t>1.62244688365071</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>228.43</t>
+          <t>2.28427091603045</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>238.57</t>
+          <t>2.38567804340551</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>255.34</t>
+          <t>2.5534432876216</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>283.1</t>
+          <t>2.83102409033624</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>272.9</t>
+          <t>2.72898541730878</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>286.59</t>
+          <t>2.86589320428112</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>291.29</t>
+          <t>2.91289752911254</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>273.71</t>
+          <t>2.73712046981538</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>311.29</t>
+          <t>3.11292797932591</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3380,84 +3385,84 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>98.56</t>
+          <t>0.985589884525345</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>94.8</t>
+          <t>0.948033458280868</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>125.44</t>
+          <t>1.25438857668043</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>95.31</t>
+          <t>0.953111881309989</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>97.85</t>
+          <t>0.97853006423017</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>92.09</t>
+          <t>0.92091914478616</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>84.85</t>
+          <t>0.848506921117678</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>87.75</t>
+          <t>0.8775078949516</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>86.51</t>
+          <t>0.865056667509228</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>91.11</t>
+          <t>0.911055315018868</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>94.28</t>
+          <t>0.942837178672189</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>116.99</t>
+          <t>1.16988759950548</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>117.78</t>
+          <t>1.17775278577605</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>111.34</t>
+          <t>1.1134369168397</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>155.33</t>
+          <t>1.55334652319246</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,84 +3472,84 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>217.04</t>
+          <t>2.17044306966418</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>223.09</t>
+          <t>2.23093651568705</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>263.58</t>
+          <t>2.63579867575155</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>183.78</t>
+          <t>1.83781253279324</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>196.38</t>
+          <t>1.96384680707255</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>155.24</t>
+          <t>1.55240055786079</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>136.39</t>
+          <t>1.36391249964746</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>198.59</t>
+          <t>1.98592194645438</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>200.24</t>
+          <t>2.00237311902364</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>242.02</t>
+          <t>2.4202295637925</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>201.42</t>
+          <t>2.01420771684379</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>213.83</t>
+          <t>2.13825317410207</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>191.69</t>
+          <t>1.91686727161334</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>175.92</t>
+          <t>1.75920527556001</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>218.88</t>
+          <t>2.18876040611926</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,84 +3559,84 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>150.62</t>
+          <t>1.50617160661234</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>137.3</t>
+          <t>1.37298228411078</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>157.23</t>
+          <t>1.5723310166486</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>1.72003255043875</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>190</t>
+          <t>1.89996603315315</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>161.36</t>
+          <t>1.61364409121076</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>168.76</t>
+          <t>1.68757940991218</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>161.89</t>
+          <t>1.61885138491786</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>142.64</t>
+          <t>1.42635463824013</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>134.9</t>
+          <t>1.34903995273976</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>129.18</t>
+          <t>1.29184268693618</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>133.07</t>
+          <t>1.33071240055536</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>115.37</t>
+          <t>1.1537456206661</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>86.47</t>
+          <t>0.864740410305353</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>83.03</t>
+          <t>0.830313677754289</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3641,84 +3646,84 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>534.26</t>
+          <t>5.34261151164397</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>492.76</t>
+          <t>4.92763719932331</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>509.65</t>
+          <t>5.09649327737962</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>510.4</t>
+          <t>5.10399750171483</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>542.22</t>
+          <t>5.42224912701902</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>521</t>
+          <t>5.20999011963246</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>507.15</t>
+          <t>5.07148012731094</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>512.98</t>
+          <t>5.12979381302793</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>432.34</t>
+          <t>4.32342872025798</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>355.01</t>
+          <t>3.55005332509927</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>361.04</t>
+          <t>3.61044513194175</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>338.42</t>
+          <t>3.38417466563925</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>273.17</t>
+          <t>2.7317022723762</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>281.93</t>
+          <t>2.8192959776664</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>214.5</t>
+          <t>2.1450443772767</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3728,84 +3733,84 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>108.35</t>
+          <t>1.08353875021367</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>114.34</t>
+          <t>1.14344564153807</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>140.1</t>
+          <t>1.40099001407831</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>129.29</t>
+          <t>1.29286644791111</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>130.98</t>
+          <t>1.30976078301587</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>132.1</t>
+          <t>1.32100165305759</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>117.54</t>
+          <t>1.17536749873982</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>117.1</t>
+          <t>1.17103191473039</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>100.07</t>
+          <t>1.00072082372353</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>1.07995604063305</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>118.09</t>
+          <t>1.18089754786991</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>122.49</t>
+          <t>1.22494227721589</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>126.6</t>
+          <t>1.26602568575699</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>70.73</t>
+          <t>0.707323504047564</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>72.39</t>
+          <t>0.723940969695169</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3815,84 +3820,84 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>88.01</t>
+          <t>0.880107982711876</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>82.06</t>
+          <t>0.820627636520103</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>108.33</t>
+          <t>1.08328710618119</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>94.21</t>
+          <t>0.942088576882582</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>94.31</t>
+          <t>0.943147349779187</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>84.54</t>
+          <t>0.845426513114116</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>84.52</t>
+          <t>0.845155141062433</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>75.75</t>
+          <t>0.757514742789056</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>62.33</t>
+          <t>0.62327957762327</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>58.9</t>
+          <t>0.58898405097452</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>56.26</t>
+          <t>0.562551152171232</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>59.25</t>
+          <t>0.592534782115846</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>55.36</t>
+          <t>0.553590510255475</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>73.23</t>
+          <t>0.732320285942316</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>94.04</t>
+          <t>0.940397107151962</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3902,84 +3907,84 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>264.99</t>
+          <t>2.64985828491068</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>233.11</t>
+          <t>2.33106979295476</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>219.23</t>
+          <t>2.19227558835332</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>216.07</t>
+          <t>2.16068456330658</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>209.72</t>
+          <t>2.09724449423553</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>255.13</t>
+          <t>2.55130042615116</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>298.07</t>
+          <t>2.98070105769992</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>355.97</t>
+          <t>3.55965467036929</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>330.09</t>
+          <t>3.30086312965534</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>289.48</t>
+          <t>2.89480131201017</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>311.5</t>
+          <t>3.11498496979896</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>326.61</t>
+          <t>3.2660539937754</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>320.14</t>
+          <t>3.20138383322121</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>131.54</t>
+          <t>1.31540422623517</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>166.24</t>
+          <t>1.66238768161214</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3989,84 +3994,84 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>123.72</t>
+          <t>1.23719522261694</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>111.72</t>
+          <t>1.1171833625892</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>136.49</t>
+          <t>1.36489988989656</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>144.09</t>
+          <t>1.4409182280558</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>145.55</t>
+          <t>1.45552143863671</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>134.38</t>
+          <t>1.34381578534081</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>129.23</t>
+          <t>1.29228339956822</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>135.76</t>
+          <t>1.3575708852097</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>138.25</t>
+          <t>1.38251702431664</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>144.12</t>
+          <t>1.44115948152121</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>148.68</t>
+          <t>1.48682269892274</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>157.84</t>
+          <t>1.57835398336894</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>185.32</t>
+          <t>1.85318040155301</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>195.41</t>
+          <t>1.95406161572549</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>229.49</t>
+          <t>2.29492725907998</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4076,84 +4081,84 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>151.15</t>
+          <t>1.51151547617612</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>154.17</t>
+          <t>1.54173376687754</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>155.17</t>
+          <t>1.55172542431666</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>144.07</t>
+          <t>1.44065955246056</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>137.7</t>
+          <t>1.37700603575676</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>117.27</t>
+          <t>1.17270234823482</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>106.51</t>
+          <t>1.06509403855577</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>100.14</t>
+          <t>1.00139595167037</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>0.951978471197756</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>92.51</t>
+          <t>0.925122895635491</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>92.96</t>
+          <t>0.929617298455002</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>97.04</t>
+          <t>0.970385447208431</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>108.4</t>
+          <t>1.08402022109955</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>117.28</t>
+          <t>1.17275018054031</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>119.13</t>
+          <t>1.19132455776522</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4163,84 +4168,84 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>0.0169303090191604</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>0.0557529826085998</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>3.81</t>
+          <t>0.0380841945697274</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>0.027800247784727</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.00835599155332378</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-0.0167831808722732</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.000275884479982613</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>0.0108222240074105</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>4.92</t>
+          <t>0.0491674526961485</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>11.16</t>
+          <t>0.111631251449643</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>10.3</t>
+          <t>0.102968674369784</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>11.09</t>
+          <t>0.11086636410285</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>19.23</t>
+          <t>0.19229294174834</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>0.216041977063292</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>23.96</t>
+          <t>0.23962308245023</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4250,84 +4255,84 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>49.14</t>
+          <t>0.491416474503729</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>54.52</t>
+          <t>0.545229787167991</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>56.76</t>
+          <t>0.567606813671574</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>56.73</t>
+          <t>0.567252599146969</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>57.14</t>
+          <t>0.57141677598991</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>54.96</t>
+          <t>0.549639710220851</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>56.2</t>
+          <t>0.562044717010826</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>57.98</t>
+          <t>0.57979855096648</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>58.03</t>
+          <t>0.580318894152746</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>60.64</t>
+          <t>0.60639268193036</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>60.34</t>
+          <t>0.603365489637898</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>61.2</t>
+          <t>0.61198168720255</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>69.21</t>
+          <t>0.692061608672368</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>70.72</t>
+          <t>0.707200816665042</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>72.44</t>
+          <t>0.724424337773727</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4339,7 +4344,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4351,7 +4356,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4363,7 +4368,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4375,7 +4380,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4387,7 +4392,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4399,7 +4404,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4411,7 +4416,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4423,7 +4428,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4470,6 +4475,11 @@
           <t>surplus_value.empe.r.pc</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4504,6 +4514,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Alternative 2</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpA2</t>
